--- a/data/compras/proveedores.xlsx
+++ b/data/compras/proveedores.xlsx
@@ -2,29 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AN0012\Documents\logo tids\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20430" windowHeight="6930"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="0" yWindow="0" windowWidth="20400" windowHeight="6540"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="146">
   <si>
     <t>ID_PROVEEDOR</t>
   </si>
@@ -53,40 +48,425 @@
     <t>TIPO DE PROVEEDOR</t>
   </si>
   <si>
-    <t>MARCELA DIAZ</t>
-  </si>
-  <si>
-    <t>PRIMER</t>
-  </si>
-  <si>
-    <t>jjcarreonc@gmail.com</t>
+    <t>PRV001</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 001</t>
+  </si>
+  <si>
+    <t>Contacto 001</t>
+  </si>
+  <si>
+    <t>+57 300 3260354</t>
+  </si>
+  <si>
+    <t>proveedor001@demo.com</t>
+  </si>
+  <si>
+    <t>Bucaramanga</t>
   </si>
   <si>
     <t>Colombia</t>
   </si>
   <si>
-    <t>Activo</t>
-  </si>
-  <si>
-    <t>Unico</t>
+    <t>ACTIVO</t>
+  </si>
+  <si>
+    <t>NACIONAL</t>
+  </si>
+  <si>
+    <t>PRV002</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 002</t>
+  </si>
+  <si>
+    <t>Contacto 002</t>
+  </si>
+  <si>
+    <t>+57 300 8656120</t>
+  </si>
+  <si>
+    <t>proveedor002@demo.com</t>
+  </si>
+  <si>
+    <t>Bogotá</t>
+  </si>
+  <si>
+    <t>MATERIA PRIMA</t>
+  </si>
+  <si>
+    <t>PRV003</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 003</t>
+  </si>
+  <si>
+    <t>Contacto 003</t>
+  </si>
+  <si>
+    <t>+57 300 4240971</t>
+  </si>
+  <si>
+    <t>proveedor003@demo.com</t>
+  </si>
+  <si>
+    <t>Cali</t>
+  </si>
+  <si>
+    <t>IMPORTADO</t>
+  </si>
+  <si>
+    <t>PRV004</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 004</t>
+  </si>
+  <si>
+    <t>Contacto 004</t>
+  </si>
+  <si>
+    <t>+57 300 1352468</t>
+  </si>
+  <si>
+    <t>proveedor004@demo.com</t>
+  </si>
+  <si>
+    <t>PRV005</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 005</t>
+  </si>
+  <si>
+    <t>Contacto 005</t>
+  </si>
+  <si>
+    <t>+57 300 5301046</t>
+  </si>
+  <si>
+    <t>proveedor005@demo.com</t>
+  </si>
+  <si>
+    <t>SERVICIOS</t>
+  </si>
+  <si>
+    <t>PRV006</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 006</t>
+  </si>
+  <si>
+    <t>Contacto 006</t>
+  </si>
+  <si>
+    <t>+57 300 6906377</t>
+  </si>
+  <si>
+    <t>proveedor006@demo.com</t>
+  </si>
+  <si>
+    <t>Barranquilla</t>
+  </si>
+  <si>
+    <t>PRV007</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 007</t>
+  </si>
+  <si>
+    <t>Contacto 007</t>
+  </si>
+  <si>
+    <t>+57 300 5562225</t>
+  </si>
+  <si>
+    <t>proveedor007@demo.com</t>
+  </si>
+  <si>
+    <t>PRV008</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 008</t>
+  </si>
+  <si>
+    <t>Contacto 008</t>
+  </si>
+  <si>
+    <t>+57 300 8285817</t>
+  </si>
+  <si>
+    <t>proveedor008@demo.com</t>
+  </si>
+  <si>
+    <t>PRV009</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 009</t>
+  </si>
+  <si>
+    <t>Contacto 009</t>
+  </si>
+  <si>
+    <t>+57 300 8052425</t>
+  </si>
+  <si>
+    <t>proveedor009@demo.com</t>
+  </si>
+  <si>
+    <t>PRV010</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 010</t>
+  </si>
+  <si>
+    <t>Contacto 010</t>
+  </si>
+  <si>
+    <t>+57 300 1005961</t>
+  </si>
+  <si>
+    <t>proveedor010@demo.com</t>
+  </si>
+  <si>
+    <t>PRV011</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 011</t>
+  </si>
+  <si>
+    <t>Contacto 011</t>
+  </si>
+  <si>
+    <t>+57 300 2822355</t>
+  </si>
+  <si>
+    <t>proveedor011@demo.com</t>
+  </si>
+  <si>
+    <t>PRV012</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 012</t>
+  </si>
+  <si>
+    <t>Contacto 012</t>
+  </si>
+  <si>
+    <t>+57 300 2050400</t>
+  </si>
+  <si>
+    <t>proveedor012@demo.com</t>
+  </si>
+  <si>
+    <t>PRV013</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 013</t>
+  </si>
+  <si>
+    <t>Contacto 013</t>
+  </si>
+  <si>
+    <t>+57 300 9561753</t>
+  </si>
+  <si>
+    <t>proveedor013@demo.com</t>
+  </si>
+  <si>
+    <t>PRV014</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 014</t>
+  </si>
+  <si>
+    <t>Contacto 014</t>
+  </si>
+  <si>
+    <t>+57 300 6956942</t>
+  </si>
+  <si>
+    <t>proveedor014@demo.com</t>
+  </si>
+  <si>
+    <t>PRV015</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 015</t>
+  </si>
+  <si>
+    <t>Contacto 015</t>
+  </si>
+  <si>
+    <t>+57 300 2489630</t>
+  </si>
+  <si>
+    <t>proveedor015@demo.com</t>
+  </si>
+  <si>
+    <t>PRV016</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 016</t>
+  </si>
+  <si>
+    <t>Contacto 016</t>
+  </si>
+  <si>
+    <t>+57 300 2390923</t>
+  </si>
+  <si>
+    <t>proveedor016@demo.com</t>
+  </si>
+  <si>
+    <t>PRV017</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 017</t>
+  </si>
+  <si>
+    <t>Contacto 017</t>
+  </si>
+  <si>
+    <t>+57 300 8267895</t>
+  </si>
+  <si>
+    <t>proveedor017@demo.com</t>
+  </si>
+  <si>
+    <t>Medellín</t>
+  </si>
+  <si>
+    <t>PRV018</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 018</t>
+  </si>
+  <si>
+    <t>Contacto 018</t>
+  </si>
+  <si>
+    <t>+57 300 1143633</t>
+  </si>
+  <si>
+    <t>proveedor018@demo.com</t>
+  </si>
+  <si>
+    <t>PRV019</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 019</t>
+  </si>
+  <si>
+    <t>Contacto 019</t>
+  </si>
+  <si>
+    <t>+57 300 9989249</t>
+  </si>
+  <si>
+    <t>proveedor019@demo.com</t>
+  </si>
+  <si>
+    <t>PRV020</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 020</t>
+  </si>
+  <si>
+    <t>Contacto 020</t>
+  </si>
+  <si>
+    <t>+57 300 7332708</t>
+  </si>
+  <si>
+    <t>proveedor020@demo.com</t>
+  </si>
+  <si>
+    <t>PRV021</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 021</t>
+  </si>
+  <si>
+    <t>Contacto 021</t>
+  </si>
+  <si>
+    <t>+57 300 2232856</t>
+  </si>
+  <si>
+    <t>proveedor021@demo.com</t>
+  </si>
+  <si>
+    <t>PRV022</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 022</t>
+  </si>
+  <si>
+    <t>Contacto 022</t>
+  </si>
+  <si>
+    <t>+57 300 7781472</t>
+  </si>
+  <si>
+    <t>proveedor022@demo.com</t>
+  </si>
+  <si>
+    <t>PRV023</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 023</t>
+  </si>
+  <si>
+    <t>Contacto 023</t>
+  </si>
+  <si>
+    <t>+57 300 1488835</t>
+  </si>
+  <si>
+    <t>proveedor023@demo.com</t>
+  </si>
+  <si>
+    <t>PRV024</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 024</t>
+  </si>
+  <si>
+    <t>Contacto 024</t>
+  </si>
+  <si>
+    <t>+57 300 6409946</t>
+  </si>
+  <si>
+    <t>proveedor024@demo.com</t>
+  </si>
+  <si>
+    <t>PRV025</t>
+  </si>
+  <si>
+    <t>Proveedor Demo 025</t>
+  </si>
+  <si>
+    <t>Contacto 025</t>
+  </si>
+  <si>
+    <t>+57 300 5404690</t>
+  </si>
+  <si>
+    <t>proveedor025@demo.com</t>
+  </si>
+  <si>
+    <t>INACTIVO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -109,20 +489,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -135,7 +512,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -145,39 +522,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -209,10 +586,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,7 +620,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -256,154 +631,182 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -436,35 +839,731 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>3104293050</v>
-      </c>
-      <c r="E2" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
         <v>14</v>
       </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D12" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>112</v>
+      </c>
+      <c r="D20" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>117</v>
+      </c>
+      <c r="D21" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>123</v>
+      </c>
+      <c r="E22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" t="s">
+        <v>104</v>
+      </c>
+      <c r="G22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C23" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" t="s">
+        <v>132</v>
+      </c>
+      <c r="D24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F24" t="s">
+        <v>104</v>
+      </c>
+      <c r="G24" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="G26" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" t="s">
+        <v>145</v>
+      </c>
+      <c r="I26" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>